--- a/research/traditional_assets/database/data/brazil/brazil_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0147</v>
+        <v>0.116</v>
       </c>
       <c r="E2">
-        <v>0.0544</v>
+        <v>0.02698</v>
       </c>
       <c r="F2">
-        <v>0.133</v>
+        <v>0.215</v>
       </c>
       <c r="G2">
-        <v>0.3435189675109105</v>
+        <v>0.2511989397976228</v>
       </c>
       <c r="H2">
-        <v>0.3435189675109105</v>
+        <v>0.2511989397976228</v>
       </c>
       <c r="I2">
-        <v>0.2969562460367787</v>
+        <v>0.2995899998619528</v>
       </c>
       <c r="J2">
-        <v>0.2369903149322964</v>
+        <v>0.263599973369705</v>
       </c>
       <c r="K2">
-        <v>1296.079</v>
+        <v>1718.72</v>
       </c>
       <c r="L2">
-        <v>0.24172460740796</v>
+        <v>0.2372644569913996</v>
       </c>
       <c r="M2">
-        <v>634.4541</v>
+        <v>1317.79</v>
       </c>
       <c r="N2">
-        <v>0.04332193703013295</v>
+        <v>0.06351468589440808</v>
       </c>
       <c r="O2">
-        <v>0.4895180772159722</v>
+        <v>0.7667275646993111</v>
       </c>
       <c r="P2">
-        <v>615.8541</v>
+        <v>1309.4</v>
       </c>
       <c r="Q2">
-        <v>0.04205188766208493</v>
+        <v>0.06311030567096269</v>
       </c>
       <c r="R2">
-        <v>0.4751671001536172</v>
+        <v>0.761846024948799</v>
       </c>
       <c r="S2">
-        <v>18.60000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="T2">
-        <v>0.02931654157487517</v>
+        <v>0.006366720038852929</v>
       </c>
       <c r="U2">
-        <v>580.381</v>
+        <v>940.48</v>
       </c>
       <c r="V2">
-        <v>0.0396297054987675</v>
+        <v>0.04532914333085918</v>
       </c>
       <c r="W2">
-        <v>0.3938210227272728</v>
+        <v>0.2362824756745912</v>
       </c>
       <c r="X2">
-        <v>0.06549467920940967</v>
+        <v>0.1079243700234933</v>
       </c>
       <c r="Y2">
-        <v>0.3283263435178631</v>
+        <v>0.1283581056510979</v>
       </c>
       <c r="Z2">
-        <v>1.707761815352912</v>
+        <v>1.593376004314756</v>
       </c>
       <c r="AA2">
-        <v>0.2484507398137788</v>
+        <v>0.8535211267605636</v>
       </c>
       <c r="AB2">
-        <v>0.065148183714762</v>
+        <v>0.1067421194480552</v>
       </c>
       <c r="AC2">
-        <v>0.1833025560990168</v>
+        <v>0.7470024168151456</v>
       </c>
       <c r="AD2">
-        <v>70.53999999999999</v>
+        <v>467.98</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>70.53999999999999</v>
+        <v>467.98</v>
       </c>
       <c r="AG2">
-        <v>-509.841</v>
+        <v>-472.5</v>
       </c>
       <c r="AH2">
-        <v>0.004793539390743453</v>
+        <v>0.02205810957692812</v>
       </c>
       <c r="AI2">
-        <v>0.01330431305686113</v>
+        <v>0.0719705707756237</v>
       </c>
       <c r="AJ2">
-        <v>-0.036068741294376</v>
+        <v>-0.02330421744684419</v>
       </c>
       <c r="AK2">
-        <v>-0.1079792081554386</v>
+        <v>-0.08495298369262302</v>
       </c>
       <c r="AL2">
-        <v>47.145</v>
+        <v>83.539</v>
       </c>
       <c r="AM2">
-        <v>42.989</v>
+        <v>65.759</v>
       </c>
       <c r="AN2">
-        <v>0.04434302669130866</v>
+        <v>0.2148471214764485</v>
       </c>
       <c r="AO2">
-        <v>33.7728285077951</v>
+        <v>25.97828559116102</v>
       </c>
       <c r="AP2">
-        <v>-0.3204974917964772</v>
+        <v>-0.2169222293636948</v>
       </c>
       <c r="AQ2">
-        <v>37.03784689106515</v>
+        <v>33.00232667771712</v>
       </c>
     </row>
     <row r="3">
@@ -725,118 +725,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0255</v>
+        <v>0.187</v>
       </c>
       <c r="G3">
-        <v>0.2576271186440678</v>
+        <v>0.203448275862069</v>
       </c>
       <c r="H3">
-        <v>0.2576271186440678</v>
+        <v>0.203448275862069</v>
       </c>
       <c r="I3">
-        <v>0.1788135593220339</v>
+        <v>0.3201970443349754</v>
       </c>
       <c r="J3">
-        <v>0.1788135593220339</v>
+        <v>0.3201970443349754</v>
       </c>
       <c r="K3">
-        <v>-0.021</v>
+        <v>3.62</v>
       </c>
       <c r="L3">
-        <v>-0.0008898305084745762</v>
+        <v>0.08916256157635467</v>
       </c>
       <c r="M3">
-        <v>0.158</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.001724890829694323</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-7.523809523809524</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.158</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.001724890829694323</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-7.523809523809524</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0.861</v>
+        <v>1.32</v>
       </c>
       <c r="V3">
-        <v>0.009399563318777292</v>
+        <v>0.01310824230387289</v>
       </c>
       <c r="W3">
-        <v>-0.000658307210031348</v>
+        <v>0.06678966789667896</v>
       </c>
       <c r="X3">
-        <v>0.06602633728975586</v>
+        <v>0.1079243700234933</v>
       </c>
       <c r="Y3">
-        <v>-0.06668464449978721</v>
+        <v>-0.04113470212681437</v>
       </c>
       <c r="Z3">
-        <v>56.86746987951868</v>
+        <v>4.328819703593132</v>
       </c>
       <c r="AA3">
-        <v>10.16867469879529</v>
+        <v>1.386075274549525</v>
       </c>
       <c r="AB3">
-        <v>0.06522979487485081</v>
+        <v>0.1067421194480552</v>
       </c>
       <c r="AC3">
-        <v>10.10344490392044</v>
+        <v>1.27933315510147</v>
       </c>
       <c r="AD3">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="AG3">
-        <v>1.579</v>
+        <v>1.26</v>
       </c>
       <c r="AH3">
-        <v>0.02594640578477244</v>
+        <v>0.02498063516653757</v>
       </c>
       <c r="AI3">
-        <v>0.04307909604519774</v>
+        <v>0.02896273013022003</v>
       </c>
       <c r="AJ3">
-        <v>0.0169458783631505</v>
+        <v>0.01235778736759514</v>
       </c>
       <c r="AK3">
-        <v>0.02830814464224887</v>
+        <v>0.01435733819507748</v>
       </c>
       <c r="AL3">
-        <v>0.152</v>
+        <v>0.2</v>
       </c>
       <c r="AM3">
-        <v>-0.3140000000000001</v>
+        <v>-1.58</v>
       </c>
       <c r="AN3">
-        <v>0.3824451410658307</v>
+        <v>0.1708609271523179</v>
       </c>
       <c r="AO3">
-        <v>27.76315789473684</v>
+        <v>65</v>
       </c>
       <c r="AP3">
-        <v>0.2474921630094044</v>
+        <v>0.08344370860927153</v>
       </c>
       <c r="AQ3">
-        <v>-13.43949044585987</v>
+        <v>-8.227848101265822</v>
       </c>
     </row>
     <row r="4">
@@ -856,49 +853,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0111</v>
+        <v>0.0565</v>
       </c>
       <c r="E4">
-        <v>-0.0218</v>
+        <v>0.058</v>
       </c>
       <c r="F4">
-        <v>0.133</v>
+        <v>0.215</v>
       </c>
       <c r="G4">
-        <v>1.014459415050937</v>
+        <v>0.7009610839766818</v>
       </c>
       <c r="H4">
-        <v>1.014459415050937</v>
+        <v>0.7009610839766818</v>
       </c>
       <c r="I4">
-        <v>0.9413955526344616</v>
+        <v>0.9368205451394359</v>
       </c>
       <c r="J4">
-        <v>0.7209633332611429</v>
+        <v>0.7526171897611001</v>
       </c>
       <c r="K4">
-        <v>668.2</v>
+        <v>1009.7</v>
       </c>
       <c r="L4">
-        <v>0.7319531164421076</v>
+        <v>0.7954151567669765</v>
       </c>
       <c r="M4">
-        <v>365.3961</v>
+        <v>725.3</v>
       </c>
       <c r="N4">
-        <v>0.04918840950393754</v>
+        <v>0.05649545886494991</v>
       </c>
       <c r="O4">
-        <v>0.5468364262196946</v>
+        <v>0.7183321778746161</v>
       </c>
       <c r="P4">
-        <v>365.3961</v>
+        <v>725.3</v>
       </c>
       <c r="Q4">
-        <v>0.04918840950393754</v>
+        <v>0.05649545886494991</v>
       </c>
       <c r="R4">
-        <v>0.5468364262196946</v>
+        <v>0.7183321778746161</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -907,31 +904,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>507.8</v>
+        <v>861.9</v>
       </c>
       <c r="V4">
-        <v>0.06835834959951538</v>
+        <v>0.06713557975417114</v>
       </c>
       <c r="W4">
-        <v>0.5904913396960058</v>
+        <v>0.7035746637864958</v>
       </c>
       <c r="X4">
-        <v>0.0651464808191107</v>
+        <v>0.1067749387845428</v>
       </c>
       <c r="Y4">
-        <v>0.5253448588768951</v>
+        <v>0.596799725001953</v>
       </c>
       <c r="Z4">
-        <v>1.13220885526479</v>
+        <v>1.368920521945433</v>
       </c>
       <c r="AA4">
-        <v>0.8162810702394858</v>
+        <v>1.03027311623287</v>
       </c>
       <c r="AB4">
-        <v>0.0651464808191107</v>
+        <v>0.1067749387845428</v>
       </c>
       <c r="AC4">
-        <v>0.7511345894203751</v>
+        <v>0.9234981774483274</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -943,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-507.8</v>
+        <v>-861.9</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -952,28 +949,28 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.07337408065658098</v>
+        <v>-0.07196713509180631</v>
       </c>
       <c r="AK4">
-        <v>-0.5476113447643697</v>
+        <v>-0.9726893127186548</v>
       </c>
       <c r="AL4">
-        <v>0.157</v>
+        <v>0.249</v>
       </c>
       <c r="AM4">
-        <v>0.157</v>
+        <v>0.249</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>5473.885350318471</v>
+        <v>4775.903614457831</v>
       </c>
       <c r="AP4">
-        <v>-0.5909461189340161</v>
+        <v>-0.7248339079976454</v>
       </c>
       <c r="AQ4">
-        <v>5473.885350318471</v>
+        <v>4775.903614457831</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Porto Seguro S.A. (BOVESPA:PSSA3)</t>
+          <t>Wiz Soluções e Corretagem de Seguros S.A. (BOVESPA:WIZS3)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,124 +990,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0405</v>
+        <v>0.116</v>
       </c>
       <c r="E5">
-        <v>0.09380000000000001</v>
-      </c>
-      <c r="F5">
-        <v>-0.0861</v>
+        <v>-0.009039999999999999</v>
       </c>
       <c r="G5">
-        <v>0.1695933683229509</v>
+        <v>0.3804817788758493</v>
       </c>
       <c r="H5">
-        <v>0.1695933683229509</v>
+        <v>0.3804817788758493</v>
       </c>
       <c r="I5">
-        <v>0.1274341492127336</v>
+        <v>0.3872760963557752</v>
       </c>
       <c r="J5">
-        <v>0.09105920085782876</v>
+        <v>0.2844718962322422</v>
       </c>
       <c r="K5">
-        <v>261.6</v>
+        <v>28.8</v>
       </c>
       <c r="L5">
-        <v>0.06415853239809682</v>
+        <v>0.1778875849289685</v>
       </c>
       <c r="M5">
-        <v>119.8</v>
+        <v>22.2</v>
       </c>
       <c r="N5">
-        <v>0.04991666666666667</v>
+        <v>0.1038353601496726</v>
       </c>
       <c r="O5">
-        <v>0.4579510703363914</v>
+        <v>0.7708333333333333</v>
       </c>
       <c r="P5">
-        <v>101.2</v>
+        <v>22.2</v>
       </c>
       <c r="Q5">
-        <v>0.04216666666666666</v>
+        <v>0.1038353601496726</v>
       </c>
       <c r="R5">
-        <v>0.3868501529051988</v>
+        <v>0.7708333333333333</v>
       </c>
       <c r="S5">
-        <v>18.60000000000001</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.1552587646076795</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>61.3</v>
+        <v>6.91</v>
       </c>
       <c r="V5">
-        <v>0.02554166666666666</v>
+        <v>0.0323199251637044</v>
       </c>
       <c r="W5">
-        <v>0.1656115472271461</v>
+        <v>0.3994452149791956</v>
       </c>
       <c r="X5">
-        <v>0.06549467920940967</v>
+        <v>0.117644570249304</v>
       </c>
       <c r="Y5">
-        <v>0.1001168680177365</v>
+        <v>0.2818006447298916</v>
       </c>
       <c r="Z5">
-        <v>2.728452890792291</v>
+        <v>3.000370644922165</v>
       </c>
       <c r="AA5">
-        <v>0.2484507398137788</v>
+        <v>0.8535211267605636</v>
       </c>
       <c r="AB5">
-        <v>0.065148183714762</v>
+        <v>0.1065187099454181</v>
       </c>
       <c r="AC5">
-        <v>0.1833025560990168</v>
+        <v>0.7470024168151456</v>
       </c>
       <c r="AD5">
-        <v>25.3</v>
+        <v>51.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>25.3</v>
+        <v>51.8</v>
       </c>
       <c r="AG5">
-        <v>-36</v>
+        <v>44.89</v>
       </c>
       <c r="AH5">
-        <v>0.01043169917123655</v>
+        <v>0.1950301204819277</v>
       </c>
       <c r="AI5">
-        <v>0.01490163741312287</v>
+        <v>0.2234685073339085</v>
       </c>
       <c r="AJ5">
-        <v>-0.01522842639593909</v>
+        <v>0.1735281611194867</v>
       </c>
       <c r="AK5">
-        <v>-0.02199816681943171</v>
+        <v>0.1996086975854862</v>
       </c>
       <c r="AL5">
-        <v>46.2</v>
+        <v>6.69</v>
       </c>
       <c r="AM5">
-        <v>46.2</v>
+        <v>2.69</v>
       </c>
       <c r="AN5">
-        <v>0.04945269741985926</v>
+        <v>0.7144827586206897</v>
       </c>
       <c r="AO5">
-        <v>11.24675324675325</v>
+        <v>9.372197309417039</v>
       </c>
       <c r="AP5">
-        <v>-0.07036747458952307</v>
+        <v>0.6191724137931035</v>
       </c>
       <c r="AQ5">
-        <v>11.24675324675325</v>
+        <v>23.3085501858736</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caixa Seguridade Participações S.A. (BOVESPA:CXSE3)</t>
+          <t>Porto Seguro S.A. (BOVESPA:PSSA3)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,119 +1123,125 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.0977</v>
+      </c>
+      <c r="E6">
+        <v>-0.00404</v>
+      </c>
       <c r="F6">
-        <v>0.251</v>
+        <v>0.163</v>
       </c>
       <c r="G6">
-        <v>0.7792068595927117</v>
+        <v>0.09095682613768961</v>
       </c>
       <c r="H6">
-        <v>0.7792068595927117</v>
+        <v>0.09095682613768961</v>
       </c>
       <c r="I6">
-        <v>0.7893890675241159</v>
+        <v>0.0721120186697783</v>
       </c>
       <c r="J6">
-        <v>0.6837535609613989</v>
+        <v>0.0721120186697783</v>
       </c>
       <c r="K6">
-        <v>332.7</v>
+        <v>205.5</v>
       </c>
       <c r="L6">
-        <v>1.782958199356913</v>
+        <v>0.03996499416569428</v>
       </c>
       <c r="M6">
-        <v>135</v>
+        <v>126.59</v>
       </c>
       <c r="N6">
-        <v>0.0300213485144992</v>
+        <v>0.04493468692318615</v>
       </c>
       <c r="O6">
-        <v>0.405770964833183</v>
+        <v>0.6160097323600974</v>
       </c>
       <c r="P6">
-        <v>135</v>
+        <v>118.2</v>
       </c>
       <c r="Q6">
-        <v>0.0300213485144992</v>
+        <v>0.04195655260542383</v>
       </c>
       <c r="R6">
-        <v>0.405770964833183</v>
+        <v>0.5751824817518248</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.06627695710561655</v>
       </c>
       <c r="U6">
-        <v>6.28</v>
+        <v>70.2</v>
       </c>
       <c r="V6">
-        <v>0.001396548656822629</v>
+        <v>0.02491835865398268</v>
       </c>
       <c r="W6">
-        <v>0.3938210227272728</v>
+        <v>0.1228699551569507</v>
       </c>
       <c r="X6">
-        <v>0.0651464808191107</v>
+        <v>0.1133614526598975</v>
       </c>
       <c r="Y6">
-        <v>0.328674541908162</v>
+        <v>0.009508502497053151</v>
       </c>
       <c r="Z6">
-        <v>0.222235455249211</v>
+        <v>3.279127606657739</v>
       </c>
       <c r="AA6">
-        <v>0.1519542838985256</v>
+        <v>0.2364645111918883</v>
       </c>
       <c r="AB6">
-        <v>0.0651464808191107</v>
+        <v>0.1059561634953013</v>
       </c>
       <c r="AC6">
-        <v>0.08680780307941491</v>
+        <v>0.130508347696587</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>413.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>413.6</v>
       </c>
       <c r="AG6">
-        <v>-6.28</v>
+        <v>343.4</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.1280178284016343</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.1828470380194518</v>
       </c>
       <c r="AJ6">
-        <v>-0.00139850173253877</v>
+        <v>0.1086502562804531</v>
       </c>
       <c r="AK6">
-        <v>-0.003159716631782322</v>
+        <v>0.1566748790948079</v>
       </c>
       <c r="AL6">
-        <v>0.09</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AM6">
-        <v>-2.49</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.126975476839237</v>
       </c>
       <c r="AO6">
-        <v>1636.666666666667</v>
+        <v>4.853403141361256</v>
       </c>
       <c r="AP6">
-        <v>-0.04263408010862186</v>
+        <v>0.9356948228882834</v>
       </c>
       <c r="AQ6">
-        <v>-59.1566265060241</v>
+        <v>4.853403141361256</v>
       </c>
     </row>
     <row r="7">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wiz Soluções e Corretagem de Seguros S.A. (BOVESPA:WIZS3)</t>
+          <t>Caixa Seguridade Participações S.A. (BOVESPA:CXSE3)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,43 +1264,46 @@
         <v>0.18</v>
       </c>
       <c r="E7">
-        <v>0.0544</v>
+        <v>0.151</v>
+      </c>
+      <c r="F7">
+        <v>0.251</v>
       </c>
       <c r="G7">
-        <v>0.4513329200247985</v>
+        <v>0.6226984126984128</v>
       </c>
       <c r="H7">
-        <v>0.4513329200247985</v>
+        <v>0.6226984126984128</v>
       </c>
       <c r="I7">
-        <v>0.3825170489770613</v>
+        <v>0.8484126984126984</v>
       </c>
       <c r="J7">
-        <v>0.2462411338212123</v>
+        <v>0.7308447230202257</v>
       </c>
       <c r="K7">
-        <v>33.6</v>
+        <v>471.1</v>
       </c>
       <c r="L7">
-        <v>0.208307501549907</v>
+        <v>0.7477777777777778</v>
       </c>
       <c r="M7">
-        <v>14.1</v>
+        <v>443.7</v>
       </c>
       <c r="N7">
-        <v>0.06178790534618755</v>
+        <v>0.09286506624249148</v>
       </c>
       <c r="O7">
-        <v>0.4196428571428571</v>
+        <v>0.9418382509021439</v>
       </c>
       <c r="P7">
-        <v>14.1</v>
+        <v>443.7</v>
       </c>
       <c r="Q7">
-        <v>0.06178790534618755</v>
+        <v>0.09286506624249148</v>
       </c>
       <c r="R7">
-        <v>0.4196428571428571</v>
+        <v>0.9418382509021439</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1309,73 +1312,70 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>4.14</v>
+        <v>0.15</v>
       </c>
       <c r="V7">
-        <v>0.01814198071866784</v>
+        <v>3.139454572092342e-05</v>
       </c>
       <c r="W7">
-        <v>0.5358851674641149</v>
+        <v>0.2362824756745912</v>
       </c>
       <c r="X7">
-        <v>0.07134154212576382</v>
+        <v>0.1067749387845428</v>
       </c>
       <c r="Y7">
-        <v>0.464543625338351</v>
+        <v>0.1295075368900485</v>
       </c>
       <c r="Z7">
-        <v>-146.6363636363635</v>
+        <v>0.3169779423603284</v>
       </c>
       <c r="AA7">
-        <v>-36.10790444123774</v>
+        <v>0.2316616564878553</v>
       </c>
       <c r="AB7">
-        <v>0.06565360643570536</v>
+        <v>0.1067749387845428</v>
       </c>
       <c r="AC7">
-        <v>-36.17355804767344</v>
+        <v>0.1248867177033125</v>
       </c>
       <c r="AD7">
-        <v>42.8</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>42.8</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>38.66</v>
+        <v>-0.15</v>
       </c>
       <c r="AH7">
-        <v>0.1579335793357934</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.3605728727885425</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0.1448699692722776</v>
+        <v>-3.139553136936843e-05</v>
       </c>
       <c r="AK7">
-        <v>0.3374650837988826</v>
+        <v>-6.90814470260437e-05</v>
       </c>
       <c r="AL7">
-        <v>0.546</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.5640000000000001</v>
+        <v>-12</v>
       </c>
       <c r="AN7">
-        <v>0.6465256797583081</v>
-      </c>
-      <c r="AO7">
-        <v>113.003663003663</v>
+        <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.5839879154078549</v>
+        <v>-0.0002806361085126286</v>
       </c>
       <c r="AQ7">
-        <v>-109.3971631205674</v>
+        <v>-44.54166666666666</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/brazil/brazil_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.116</v>
+        <v>0.138</v>
       </c>
       <c r="E2">
-        <v>0.02698</v>
+        <v>0.138</v>
       </c>
       <c r="F2">
-        <v>0.215</v>
+        <v>0.161</v>
       </c>
       <c r="G2">
-        <v>0.2511989397976228</v>
+        <v>0.2577726361889809</v>
       </c>
       <c r="H2">
-        <v>0.2511989397976228</v>
+        <v>0.2577726361889809</v>
       </c>
       <c r="I2">
-        <v>0.2995899998619528</v>
+        <v>0.3489577953601752</v>
       </c>
       <c r="J2">
-        <v>0.263599973369705</v>
+        <v>0.282931362175968</v>
       </c>
       <c r="K2">
-        <v>1718.72</v>
+        <v>2658.7</v>
       </c>
       <c r="L2">
-        <v>0.2372644569913996</v>
+        <v>0.2746193732311443</v>
       </c>
       <c r="M2">
-        <v>1317.79</v>
+        <v>2110.659</v>
       </c>
       <c r="N2">
-        <v>0.06351468589440808</v>
+        <v>0.08097364382720786</v>
       </c>
       <c r="O2">
-        <v>0.7667275646993111</v>
+        <v>0.7938688080640915</v>
       </c>
       <c r="P2">
-        <v>1309.4</v>
+        <v>2073.04</v>
       </c>
       <c r="Q2">
-        <v>0.06311030567096269</v>
+        <v>0.07953042277296095</v>
       </c>
       <c r="R2">
-        <v>0.761846024948799</v>
+        <v>0.779719411742581</v>
       </c>
       <c r="S2">
-        <v>8.390000000000001</v>
+        <v>37.61900000000009</v>
       </c>
       <c r="T2">
-        <v>0.006366720038852929</v>
+        <v>0.01782334332547327</v>
       </c>
       <c r="U2">
-        <v>940.48</v>
+        <v>719.1120000000001</v>
       </c>
       <c r="V2">
-        <v>0.04532914333085918</v>
+        <v>0.0275881224583749</v>
       </c>
       <c r="W2">
-        <v>0.2362824756745912</v>
+        <v>0.2428393524283935</v>
       </c>
       <c r="X2">
-        <v>0.1079243700234933</v>
+        <v>0.09710067976613021</v>
       </c>
       <c r="Y2">
-        <v>0.1283581056510979</v>
+        <v>0.1457386726622633</v>
       </c>
       <c r="Z2">
-        <v>1.593376004314756</v>
+        <v>1.884677529249158</v>
       </c>
       <c r="AA2">
-        <v>0.8535211267605636</v>
+        <v>0.7061001369453289</v>
       </c>
       <c r="AB2">
-        <v>0.1067421194480552</v>
+        <v>0.09464915364447084</v>
       </c>
       <c r="AC2">
-        <v>0.7470024168151456</v>
+        <v>0.6118896155890633</v>
       </c>
       <c r="AD2">
-        <v>467.98</v>
+        <v>319.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>467.98</v>
+        <v>319.2</v>
       </c>
       <c r="AG2">
-        <v>-472.5</v>
+        <v>-399.912</v>
       </c>
       <c r="AH2">
-        <v>0.02205810957692812</v>
+        <v>0.01209769112987584</v>
       </c>
       <c r="AI2">
-        <v>0.0719705707756237</v>
+        <v>0.0415397829312095</v>
       </c>
       <c r="AJ2">
-        <v>-0.02330421744684419</v>
+        <v>-0.01558133830134144</v>
       </c>
       <c r="AK2">
-        <v>-0.08495298369262302</v>
+        <v>-0.05741664714071094</v>
       </c>
       <c r="AL2">
-        <v>83.539</v>
+        <v>81.39400000000001</v>
       </c>
       <c r="AM2">
-        <v>65.759</v>
+        <v>45.21400000000001</v>
       </c>
       <c r="AN2">
-        <v>0.2148471214764485</v>
+        <v>0.09323246779799634</v>
       </c>
       <c r="AO2">
-        <v>25.97828559116102</v>
+        <v>41.50674496891663</v>
       </c>
       <c r="AP2">
-        <v>-0.2169222293636948</v>
+        <v>-0.1168069632269183</v>
       </c>
       <c r="AQ2">
-        <v>33.00232667771712</v>
+        <v>74.72021940107045</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alper Consultoria e Corretora de Seguros S.A. (BOVESPA:APER3)</t>
+          <t>BB Seguridade Participações S.A. (BOVESPA:BBSE3)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,115 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.187</v>
+        <v>0.138</v>
+      </c>
+      <c r="E3">
+        <v>0.149</v>
+      </c>
+      <c r="F3">
+        <v>0.109</v>
       </c>
       <c r="G3">
-        <v>0.203448275862069</v>
+        <v>0.7463861137467209</v>
       </c>
       <c r="H3">
-        <v>0.203448275862069</v>
+        <v>0.7463861137467209</v>
       </c>
       <c r="I3">
-        <v>0.3201970443349754</v>
+        <v>0.9509962605346878</v>
       </c>
       <c r="J3">
-        <v>0.3201970443349754</v>
+        <v>0.7802376961053655</v>
       </c>
       <c r="K3">
-        <v>3.62</v>
+        <v>1494.5</v>
       </c>
       <c r="L3">
-        <v>0.08916256157635467</v>
+        <v>0.8341240162973712</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1430.2</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1032985923020809</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.9569755771160924</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1393.8</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1006695412883794</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.9326196052191368</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>36.40000000000009</v>
+      </c>
+      <c r="T3">
+        <v>0.02545098587610131</v>
       </c>
       <c r="U3">
-        <v>1.32</v>
+        <v>674.2</v>
       </c>
       <c r="V3">
-        <v>0.01310824230387289</v>
+        <v>0.04869522509443638</v>
       </c>
       <c r="W3">
-        <v>0.06678966789667896</v>
+        <v>0.8549771167048055</v>
       </c>
       <c r="X3">
-        <v>0.1079243700234933</v>
+        <v>0.09482543898818621</v>
       </c>
       <c r="Y3">
-        <v>-0.04113470212681437</v>
+        <v>0.7601516777166193</v>
       </c>
       <c r="Z3">
-        <v>4.328819703593132</v>
+        <v>2.022006545536621</v>
       </c>
       <c r="AA3">
-        <v>1.386075274549525</v>
+        <v>1.577645728599462</v>
       </c>
       <c r="AB3">
-        <v>0.1067421194480552</v>
+        <v>0.09482543898818621</v>
       </c>
       <c r="AC3">
-        <v>1.27933315510147</v>
+        <v>1.482820289611276</v>
       </c>
       <c r="AD3">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.26</v>
+        <v>-674.2</v>
       </c>
       <c r="AH3">
-        <v>0.02498063516653757</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.02896273013022003</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.01235778736759514</v>
+        <v>-0.05118782789592366</v>
       </c>
       <c r="AK3">
-        <v>0.01435733819507748</v>
+        <v>-0.4614647501711158</v>
       </c>
       <c r="AL3">
-        <v>0.2</v>
+        <v>0.323</v>
       </c>
       <c r="AM3">
-        <v>-1.58</v>
+        <v>0.323</v>
       </c>
       <c r="AN3">
-        <v>0.1708609271523179</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>65</v>
+        <v>5275.232198142415</v>
       </c>
       <c r="AP3">
-        <v>0.08344370860927153</v>
+        <v>-0.3956804976817889</v>
       </c>
       <c r="AQ3">
-        <v>-8.227848101265822</v>
+        <v>5275.232198142415</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BB Seguridade Participações S.A. (BOVESPA:BBSE3)</t>
+          <t>Alper Consultoria e Corretora de Seguros S.A. (BOVESPA:APER3)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,124 +862,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0565</v>
-      </c>
-      <c r="E4">
-        <v>0.058</v>
-      </c>
-      <c r="F4">
-        <v>0.215</v>
+        <v>0.276</v>
       </c>
       <c r="G4">
-        <v>0.7009610839766818</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="H4">
-        <v>0.7009610839766818</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="I4">
-        <v>0.9368205451394359</v>
+        <v>0.1902356902356903</v>
       </c>
       <c r="J4">
-        <v>0.7526171897611001</v>
+        <v>0.1902356902356903</v>
       </c>
       <c r="K4">
-        <v>1009.7</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>0.7954151567669765</v>
+        <v>0.0505050505050505</v>
       </c>
       <c r="M4">
-        <v>725.3</v>
+        <v>2.425</v>
       </c>
       <c r="N4">
-        <v>0.05649545886494991</v>
+        <v>0.01382554161915621</v>
       </c>
       <c r="O4">
-        <v>0.7183321778746161</v>
+        <v>0.8083333333333332</v>
       </c>
       <c r="P4">
-        <v>725.3</v>
+        <v>1.44</v>
       </c>
       <c r="Q4">
-        <v>0.05649545886494991</v>
+        <v>0.008209806157354617</v>
       </c>
       <c r="R4">
-        <v>0.7183321778746161</v>
+        <v>0.48</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.9849999999999999</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.4061855670103093</v>
       </c>
       <c r="U4">
-        <v>861.9</v>
+        <v>0.512</v>
       </c>
       <c r="V4">
-        <v>0.06713557975417114</v>
+        <v>0.002919042189281642</v>
       </c>
       <c r="W4">
-        <v>0.7035746637864958</v>
+        <v>0.03468208092485549</v>
       </c>
       <c r="X4">
-        <v>0.1067749387845428</v>
+        <v>0.09746061499532724</v>
       </c>
       <c r="Y4">
-        <v>0.596799725001953</v>
+        <v>-0.06277853407047175</v>
       </c>
       <c r="Z4">
-        <v>1.368920521945433</v>
+        <v>4.107883817427384</v>
       </c>
       <c r="AA4">
-        <v>1.03027311623287</v>
+        <v>0.7814661134163206</v>
       </c>
       <c r="AB4">
-        <v>0.1067749387845428</v>
+        <v>0.09464915364447084</v>
       </c>
       <c r="AC4">
-        <v>0.9234981774483274</v>
+        <v>0.6868169597718498</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG4">
-        <v>-861.9</v>
+        <v>11.988</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.06652474720596062</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.1155268022181146</v>
       </c>
       <c r="AJ4">
-        <v>-0.07196713509180631</v>
+        <v>0.06397421393045445</v>
       </c>
       <c r="AK4">
-        <v>-0.9726893127186548</v>
+        <v>0.1113215957209717</v>
       </c>
       <c r="AL4">
-        <v>0.249</v>
+        <v>0.526</v>
       </c>
       <c r="AM4">
-        <v>0.249</v>
+        <v>-2.024</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.7961783439490446</v>
       </c>
       <c r="AO4">
-        <v>4775.903614457831</v>
+        <v>21.48288973384031</v>
       </c>
       <c r="AP4">
-        <v>-0.7248339079976454</v>
+        <v>0.7635668789808917</v>
       </c>
       <c r="AQ4">
-        <v>4775.903614457831</v>
+        <v>-5.58300395256917</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wiz Soluções e Corretagem de Seguros S.A. (BOVESPA:WIZS3)</t>
+          <t>Wiz Co Participações e Corretagem de Seguros S.A. (BOVESPA:WIZC3)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,121 +993,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.116</v>
+        <v>0.132</v>
       </c>
       <c r="E5">
-        <v>-0.009039999999999999</v>
+        <v>-0.0958</v>
       </c>
       <c r="G5">
-        <v>0.3804817788758493</v>
+        <v>0.3747028055159296</v>
       </c>
       <c r="H5">
-        <v>0.3804817788758493</v>
+        <v>0.3747028055159296</v>
       </c>
       <c r="I5">
-        <v>0.3872760963557752</v>
+        <v>0.3466476462196862</v>
       </c>
       <c r="J5">
-        <v>0.2844718962322422</v>
+        <v>0.2313040343992568</v>
       </c>
       <c r="K5">
-        <v>28.8</v>
+        <v>19.5</v>
       </c>
       <c r="L5">
-        <v>0.1778875849289685</v>
+        <v>0.09272467902995719</v>
       </c>
       <c r="M5">
-        <v>22.2</v>
+        <v>33.834</v>
       </c>
       <c r="N5">
-        <v>0.1038353601496726</v>
+        <v>0.1412103505843072</v>
       </c>
       <c r="O5">
-        <v>0.7708333333333333</v>
+        <v>1.735076923076923</v>
       </c>
       <c r="P5">
-        <v>22.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q5">
-        <v>0.1038353601496726</v>
+        <v>0.1402337228714524</v>
       </c>
       <c r="R5">
-        <v>0.7708333333333333</v>
+        <v>1.723076923076923</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.2340000000000018</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.006916119879411295</v>
       </c>
       <c r="U5">
-        <v>6.91</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="V5">
-        <v>0.0323199251637044</v>
+        <v>0.0335559265442404</v>
       </c>
       <c r="W5">
-        <v>0.3994452149791956</v>
+        <v>0.2428393524283935</v>
       </c>
       <c r="X5">
-        <v>0.117644570249304</v>
+        <v>0.1059987260358135</v>
       </c>
       <c r="Y5">
-        <v>0.2818006447298916</v>
+        <v>0.13684062639258</v>
       </c>
       <c r="Z5">
-        <v>3.000370644922165</v>
+        <v>3.052692698504863</v>
       </c>
       <c r="AA5">
-        <v>0.8535211267605636</v>
+        <v>0.7061001369453289</v>
       </c>
       <c r="AB5">
-        <v>0.1065187099454181</v>
+        <v>0.09421052135626559</v>
       </c>
       <c r="AC5">
-        <v>0.7470024168151456</v>
+        <v>0.6118896155890633</v>
       </c>
       <c r="AD5">
-        <v>51.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>51.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AG5">
-        <v>44.89</v>
+        <v>64.36000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.1950301204819277</v>
+        <v>0.2320512820512821</v>
       </c>
       <c r="AI5">
-        <v>0.2234685073339085</v>
+        <v>0.2764413898434517</v>
       </c>
       <c r="AJ5">
-        <v>0.1735281611194867</v>
+        <v>0.2117383866298197</v>
       </c>
       <c r="AK5">
-        <v>0.1996086975854862</v>
+        <v>0.2535255652721973</v>
       </c>
       <c r="AL5">
-        <v>6.69</v>
+        <v>14</v>
       </c>
       <c r="AM5">
-        <v>2.69</v>
+        <v>7.77</v>
       </c>
       <c r="AN5">
-        <v>0.7144827586206897</v>
+        <v>0.7886710239651417</v>
       </c>
       <c r="AO5">
-        <v>9.372197309417039</v>
+        <v>5.207142857142857</v>
       </c>
       <c r="AP5">
-        <v>0.6191724137931035</v>
+        <v>0.7010893246187365</v>
       </c>
       <c r="AQ5">
-        <v>23.3085501858736</v>
+        <v>9.382239382239383</v>
       </c>
     </row>
     <row r="6">
@@ -1124,124 +1127,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0977</v>
+        <v>0.117</v>
       </c>
       <c r="E6">
-        <v>-0.00404</v>
+        <v>0.127</v>
       </c>
       <c r="F6">
-        <v>0.163</v>
+        <v>0.237</v>
       </c>
       <c r="G6">
-        <v>0.09095682613768961</v>
+        <v>0.07325822709753928</v>
       </c>
       <c r="H6">
-        <v>0.09095682613768961</v>
+        <v>0.07325822709753928</v>
       </c>
       <c r="I6">
-        <v>0.0721120186697783</v>
+        <v>0.1276756596501631</v>
       </c>
       <c r="J6">
-        <v>0.0721120186697783</v>
+        <v>0.08957969957847473</v>
       </c>
       <c r="K6">
-        <v>205.5</v>
+        <v>435.2</v>
       </c>
       <c r="L6">
-        <v>0.03996499416569428</v>
+        <v>0.064512303587311</v>
       </c>
       <c r="M6">
-        <v>126.59</v>
+        <v>125.8</v>
       </c>
       <c r="N6">
-        <v>0.04493468692318615</v>
+        <v>0.03303744944587426</v>
       </c>
       <c r="O6">
-        <v>0.6160097323600974</v>
+        <v>0.2890625</v>
       </c>
       <c r="P6">
-        <v>118.2</v>
+        <v>125.8</v>
       </c>
       <c r="Q6">
-        <v>0.04195655260542383</v>
+        <v>0.03303744944587426</v>
       </c>
       <c r="R6">
-        <v>0.5751824817518248</v>
+        <v>0.2890625</v>
       </c>
       <c r="S6">
-        <v>8.390000000000001</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.06627695710561655</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>70.2</v>
+        <v>36.3</v>
       </c>
       <c r="V6">
-        <v>0.02491835865398268</v>
+        <v>0.009533063711329375</v>
       </c>
       <c r="W6">
-        <v>0.1228699551569507</v>
+        <v>0.2366374857267142</v>
       </c>
       <c r="X6">
-        <v>0.1133614526598975</v>
+        <v>0.09710067976613021</v>
       </c>
       <c r="Y6">
-        <v>0.009508502497053151</v>
+        <v>0.139536805960584</v>
       </c>
       <c r="Z6">
-        <v>3.279127606657739</v>
+        <v>3.379590200891739</v>
       </c>
       <c r="AA6">
-        <v>0.2364645111918883</v>
+        <v>0.3027426748942391</v>
       </c>
       <c r="AB6">
-        <v>0.1059561634953013</v>
+        <v>0.09444948772189375</v>
       </c>
       <c r="AC6">
-        <v>0.130508347696587</v>
+        <v>0.2082931871723453</v>
       </c>
       <c r="AD6">
-        <v>413.6</v>
+        <v>234.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>413.6</v>
+        <v>234.3</v>
       </c>
       <c r="AG6">
-        <v>343.4</v>
+        <v>198</v>
       </c>
       <c r="AH6">
-        <v>0.1280178284016343</v>
+        <v>0.05796491922515524</v>
       </c>
       <c r="AI6">
-        <v>0.1828470380194518</v>
+        <v>0.08929796478390122</v>
       </c>
       <c r="AJ6">
-        <v>0.1086502562804531</v>
+        <v>0.04942832892306156</v>
       </c>
       <c r="AK6">
-        <v>0.1566748790948079</v>
+        <v>0.07652173913043478</v>
       </c>
       <c r="AL6">
-        <v>76.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="AM6">
-        <v>76.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="AN6">
-        <v>1.126975476839237</v>
+        <v>0.2652552926525529</v>
       </c>
       <c r="AO6">
-        <v>4.853403141361256</v>
+        <v>12.95187969924812</v>
       </c>
       <c r="AP6">
-        <v>0.9356948228882834</v>
+        <v>0.224159402241594</v>
       </c>
       <c r="AQ6">
-        <v>4.853403141361256</v>
+        <v>12.95187969924812</v>
       </c>
     </row>
     <row r="7">
@@ -1261,49 +1264,49 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.18</v>
+        <v>0.212</v>
       </c>
       <c r="E7">
-        <v>0.151</v>
+        <v>0.207</v>
       </c>
       <c r="F7">
-        <v>0.251</v>
+        <v>0.161</v>
       </c>
       <c r="G7">
-        <v>0.6226984126984128</v>
+        <v>0.6545766590389016</v>
       </c>
       <c r="H7">
-        <v>0.6226984126984128</v>
+        <v>0.6545766590389016</v>
       </c>
       <c r="I7">
-        <v>0.8484126984126984</v>
+        <v>0.834096109839817</v>
       </c>
       <c r="J7">
-        <v>0.7308447230202257</v>
+        <v>0.7211817527427744</v>
       </c>
       <c r="K7">
-        <v>471.1</v>
+        <v>706.5</v>
       </c>
       <c r="L7">
-        <v>0.7477777777777778</v>
+        <v>0.8083524027459954</v>
       </c>
       <c r="M7">
-        <v>443.7</v>
+        <v>518.4</v>
       </c>
       <c r="N7">
-        <v>0.09286506624249148</v>
+        <v>0.06481701446629741</v>
       </c>
       <c r="O7">
-        <v>0.9418382509021439</v>
+        <v>0.7337579617834394</v>
       </c>
       <c r="P7">
-        <v>443.7</v>
+        <v>518.4</v>
       </c>
       <c r="Q7">
-        <v>0.09286506624249148</v>
+        <v>0.06481701446629741</v>
       </c>
       <c r="R7">
-        <v>0.9418382509021439</v>
+        <v>0.7337579617834394</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1312,31 +1315,31 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="V7">
-        <v>3.139454572092342e-05</v>
+        <v>7.50196926693257e-06</v>
       </c>
       <c r="W7">
-        <v>0.2362824756745912</v>
+        <v>0.3253511397651393</v>
       </c>
       <c r="X7">
-        <v>0.1067749387845428</v>
+        <v>0.09482543898818621</v>
       </c>
       <c r="Y7">
-        <v>0.1295075368900485</v>
+        <v>0.2305257007769531</v>
       </c>
       <c r="Z7">
-        <v>0.3169779423603284</v>
+        <v>0.402514564671748</v>
       </c>
       <c r="AA7">
-        <v>0.2316616564878553</v>
+        <v>0.290286159254466</v>
       </c>
       <c r="AB7">
-        <v>0.1067749387845428</v>
+        <v>0.09482543898818621</v>
       </c>
       <c r="AC7">
-        <v>0.1248867177033125</v>
+        <v>0.1954607202662798</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1348,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1357,25 +1360,28 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-3.139553136936843e-05</v>
+        <v>-7.502025546897663e-06</v>
       </c>
       <c r="AK7">
-        <v>-6.90814470260437e-05</v>
+        <v>-2.348299830922412e-05</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AM7">
-        <v>-12</v>
+        <v>-27.355</v>
       </c>
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>16200</v>
+      </c>
       <c r="AP7">
-        <v>-0.0002806361085126286</v>
+        <v>-8.230452674897119e-05</v>
       </c>
       <c r="AQ7">
-        <v>-44.54166666666666</v>
+        <v>-26.64960701882654</v>
       </c>
     </row>
   </sheetData>
